--- a/Data/microtech_corporate_tax_adjustments_2025.xlsx
+++ b/Data/microtech_corporate_tax_adjustments_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prita\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ECE591-7255-4798-905D-C11688990E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9F908B-07AD-4FE7-8B77-39252647B491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Guide" sheetId="5" r:id="rId1"/>
@@ -539,30 +539,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Subject</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: ABC Inc. Tax Return Updates &amp; Insights</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Account Types </t>
   </si>
   <si>
@@ -693,6 +669,9 @@
   </si>
   <si>
     <t>Chart of Accounts – Quick Reference Guide</t>
+  </si>
+  <si>
+    <t>Subject: Microtech Inc. Tax Return Updates &amp; Insights</t>
   </si>
 </sst>
 </file>
@@ -1277,6 +1256,9 @@
     <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1290,9 +1272,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1533,42 +1512,42 @@
     <row r="1" spans="2:2" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:2" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="86" t="s">
-        <v>143</v>
+      <c r="B3" s="80" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="74" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
@@ -1578,12 +1557,12 @@
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
@@ -1593,62 +1572,62 @@
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="74" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="80" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="86" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -1677,28 +1656,28 @@
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
@@ -4058,10 +4037,10 @@
     </row>
     <row r="63" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
-      <c r="B63" s="82" t="s">
+      <c r="B63" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="83"/>
+      <c r="C63" s="84"/>
       <c r="D63" s="15" t="s">
         <v>72</v>
       </c>
@@ -4075,10 +4054,10 @@
       <c r="B64" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C64" s="84" t="s">
+      <c r="C64" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="D64" s="85"/>
+      <c r="D64" s="86"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -4792,7 +4771,7 @@
     </row>
     <row r="7" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
